--- a/data/trans_dic/IP13-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,97%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 11,6</t>
+          <t>4,14; 11,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,8</t>
+          <t>4,66; 12,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,95</t>
+          <t>1,83; 7,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 12,9</t>
+          <t>2,04; 12,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,99</t>
+          <t>3,54; 11,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 12,85</t>
+          <t>5,42; 13,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,85</t>
+          <t>4,29; 11,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 12,17</t>
+          <t>3,07; 12,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,95</t>
+          <t>4,68; 10,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,24</t>
+          <t>5,83; 11,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 8,35</t>
+          <t>3,79; 8,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,35</t>
+          <t>3,2; 10,52</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,42%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,76</t>
+          <t>2,88; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,41</t>
+          <t>4,61; 9,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,81</t>
+          <t>2,73; 6,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,46</t>
+          <t>4,95; 11,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,06</t>
+          <t>2,7; 6,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,87</t>
+          <t>2,71; 7,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,61</t>
+          <t>4,61; 9,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,54</t>
+          <t>3,17; 9,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,23</t>
+          <t>3,32; 6,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,91</t>
+          <t>4,24; 7,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,4</t>
+          <t>4,19; 7,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 9,19</t>
+          <t>4,88; 9,14</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,93%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,92%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,6</t>
+          <t>3,82; 10,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,13</t>
+          <t>0,85; 5,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,32</t>
+          <t>2,85; 8,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,93</t>
+          <t>4,84; 11,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,56</t>
+          <t>1,06; 6,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,3</t>
+          <t>2,1; 7,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,26</t>
+          <t>2,1; 7,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 11,38</t>
+          <t>3,62; 10,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,34</t>
+          <t>3,07; 7,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,33</t>
+          <t>2,03; 5,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,89</t>
+          <t>3,05; 6,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,61</t>
+          <t>4,93; 9,76</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,92</t>
+          <t>1,63; 6,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,38</t>
+          <t>3,71; 9,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,3</t>
+          <t>1,96; 7,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,83</t>
+          <t>2,99; 8,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,4</t>
+          <t>2,33; 7,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,41</t>
+          <t>2,8; 8,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,85</t>
+          <t>1,36; 6,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,32</t>
+          <t>3,6; 8,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,34</t>
+          <t>2,44; 5,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,97</t>
+          <t>3,9; 8,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,6</t>
+          <t>2,13; 5,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,87</t>
+          <t>3,84; 7,2</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,77</t>
+          <t>3,79; 6,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,12</t>
+          <t>4,81; 7,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,7</t>
+          <t>3,27; 5,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,1</t>
+          <t>5,11; 8,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,3</t>
+          <t>3,22; 5,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,77</t>
+          <t>4,19; 7,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,79</t>
+          <t>4,03; 6,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,08</t>
+          <t>4,46; 7,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,71</t>
+          <t>3,84; 5,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,96</t>
+          <t>4,8; 6,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,77</t>
+          <t>4,04; 5,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 7,18</t>
+          <t>5,13; 7,51</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8612</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11744</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4988</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7398</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>12427</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>9565</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8612</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11744</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4988</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>6374</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3851; 12315</t>
+          <t>5030; 13922</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7881; 18709</t>
+          <t>6714; 18161</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5506; 14414</t>
+          <t>2272; 9719</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1625; 7420</t>
+          <t>1032; 6215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4761; 14557</t>
+          <t>3753; 12099</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7005; 18496</t>
+          <t>7921; 19422</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2304; 9746</t>
+          <t>5651; 15583</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1038; 7476</t>
+          <t>1600; 6581</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10801; 22644</t>
+          <t>10643; 22882</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16394; 32620</t>
+          <t>16926; 32746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9441; 21367</t>
+          <t>9685; 21939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4070; 12313</t>
+          <t>3284; 10795</t>
         </is>
       </c>
     </row>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11814</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18879</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11962</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11186</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11051</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14336</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9081</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11814</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18879</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11425</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>20273</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6578; 17109</t>
+          <t>7300; 18296</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6316; 17470</t>
+          <t>12403; 26798</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9407; 20650</t>
+          <t>7052; 17679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5113; 15064</t>
+          <t>7764; 17835</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6831; 17917</t>
+          <t>6843; 17325</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12882; 26562</t>
+          <t>6381; 17728</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6331; 17068</t>
+          <t>9705; 20706</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9140; 20975</t>
+          <t>4606; 14084</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16104; 31599</t>
+          <t>16851; 31132</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22039; 39894</t>
+          <t>21380; 38673</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19156; 34667</t>
+          <t>19643; 34725</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16828; 31336</t>
+          <t>14759; 27660</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9191</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4403</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9688</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15784</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3737</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6161</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>7556</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10549</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9191</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4403</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9688</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26326</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1403; 8418</t>
+          <t>5410; 15284</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2806; 11200</t>
+          <t>1341; 9312</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3919; 13821</t>
+          <t>5382; 16710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6044; 17190</t>
+          <t>9685; 23277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5273; 14942</t>
+          <t>1353; 8088</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1833; 9994</t>
+          <t>3291; 11138</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5296; 15567</t>
+          <t>3958; 13217</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9862; 24171</t>
+          <t>6315; 17731</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8370; 19743</t>
+          <t>8266; 20087</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5950; 16825</t>
+          <t>6395; 17353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11831; 25998</t>
+          <t>11504; 26199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18197; 37071</t>
+          <t>18493; 36575</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6513</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6785</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15007</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8089</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8983</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5609</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13839</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6513</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11074</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6785</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>29436</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4577; 13435</t>
+          <t>3354; 12441</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5230; 14356</t>
+          <t>6637; 17734</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2438; 10910</t>
+          <t>3416; 12513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8319; 21573</t>
+          <t>8751; 23520</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3233; 11117</t>
+          <t>4515; 13798</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6599; 16836</t>
+          <t>4795; 15168</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3040; 11926</t>
+          <t>2355; 10667</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8480; 22366</t>
+          <t>9225; 22406</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9154; 21356</t>
+          <t>9748; 21197</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13890; 27930</t>
+          <t>13659; 28852</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6922; 19458</t>
+          <t>7393; 19838</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20578; 39900</t>
+          <t>21102; 39532</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36130</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>45633</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>30410</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>38621</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>37065</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37437</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36130</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>46100</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>32886</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>82409</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22650; 39327</t>
+          <t>27358; 46481</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29857; 50555</t>
+          <t>36103; 57724</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28561; 47171</t>
+          <t>24341; 43080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28000; 47236</t>
+          <t>35761; 58317</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27185; 45549</t>
+          <t>21917; 39561</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36046; 58334</t>
+          <t>29760; 50695</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24044; 43119</t>
+          <t>28392; 46841</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37418; 61482</t>
+          <t>28041; 47758</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54060; 80167</t>
+          <t>53897; 78900</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71740; 101689</t>
+          <t>70068; 100074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57615; 83620</t>
+          <t>58617; 86489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71550; 102444</t>
+          <t>68193; 99884</t>
         </is>
       </c>
     </row>
